--- a/data/warn-scraper/cache/ky/latest.xlsx
+++ b/data/warn-scraper/cache/ky/latest.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeff.lee\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4864B7E3-A28F-409C-8F5A-BB93E67484A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ED3394FF-1FAC-43F0-9BFF-C3F5001E92D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{EAB8D913-CB4E-4E9F-A882-46BBF92D3929}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B2010329-5A2A-4F17-89E7-EB888C9792EE}"/>
   </bookViews>
   <sheets>
-    <sheet name="WARN-Notice Report 09092026" sheetId="1" r:id="rId1"/>
+    <sheet name="WARN Report-2026-09-16-09-00-01" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="134">
   <si>
     <t>Company: Company Name</t>
   </si>
@@ -61,12 +61,30 @@
     <t>Workforce Board</t>
   </si>
   <si>
+    <t>PARSONS CORPORATION</t>
+  </si>
+  <si>
+    <t>WARN Notice</t>
+  </si>
+  <si>
+    <t>Notice 2839</t>
+  </si>
+  <si>
+    <t>Closure</t>
+  </si>
+  <si>
+    <t>Madison</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000Wx8De/kpztXs6KnqOtbjTf8oju8WFuUrtiWuyutIsdc8uDFhE</t>
+  </si>
+  <si>
+    <t>Bluegrass</t>
+  </si>
+  <si>
     <t>Congo Brands (Alani, Prime, 3D Energy)</t>
   </si>
   <si>
-    <t>WARN Notice</t>
-  </si>
-  <si>
     <t>Notice 2837</t>
   </si>
   <si>
@@ -94,9 +112,6 @@
     <t>Notice 2833</t>
   </si>
   <si>
-    <t>Closure</t>
-  </si>
-  <si>
     <t>Out of the State County</t>
   </si>
   <si>
@@ -112,18 +127,12 @@
     <t>Notice 2820</t>
   </si>
   <si>
-    <t>Madison</t>
-  </si>
-  <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000CLJC1/DbyYp68sVwKoN.GQkRf5EyzUntPUC3BOkVG9L_FcJUc</t>
   </si>
   <si>
     <t>No</t>
   </si>
   <si>
-    <t>Bluegrass</t>
-  </si>
-  <si>
     <t>Geodis</t>
   </si>
   <si>
@@ -302,9 +311,6 @@
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000N9QpF/4EEzN4tM6NejTIykMYCa83PGBw3SZK1mgoh_UyK2LBY</t>
-  </si>
-  <si>
-    <t>PARSONS CORPORATION</t>
   </si>
   <si>
     <t>Notice 2751</t>
@@ -1276,8 +1282,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40372AC9-E032-45DE-9B69-B370B53C7216}">
-  <dimension ref="A1:M35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14C42207-125F-4EBA-BB4D-58BF2CFC4ED5}">
+  <dimension ref="A1:M36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1338,63 +1344,60 @@
         <v>17</v>
       </c>
       <c r="F2" s="1">
-        <v>46269</v>
+        <v>46275</v>
       </c>
       <c r="G2">
-        <v>312111</v>
+        <v>541330</v>
       </c>
       <c r="H2" t="s">
         <v>18</v>
       </c>
       <c r="I2">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="J2" s="1">
-        <v>46330</v>
-      </c>
-      <c r="K2" t="s">
+        <v>46345</v>
+      </c>
+      <c r="M2" t="s">
         <v>19</v>
-      </c>
-      <c r="L2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
         <v>22</v>
       </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>23</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" s="1">
+        <v>46269</v>
+      </c>
+      <c r="G3">
+        <v>312111</v>
+      </c>
+      <c r="H3" t="s">
         <v>24</v>
       </c>
-      <c r="E3" t="s">
+      <c r="I3">
+        <v>15</v>
+      </c>
+      <c r="J3" s="1">
+        <v>46330</v>
+      </c>
+      <c r="K3" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="1">
-        <v>46244</v>
-      </c>
-      <c r="G3">
-        <v>522110</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="L3" t="s">
         <v>26</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3" s="1">
-        <v>46304</v>
-      </c>
-      <c r="K3" t="s">
-        <v>19</v>
       </c>
       <c r="M3" t="s">
         <v>27</v>
@@ -1411,16 +1414,16 @@
         <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
         <v>30</v>
       </c>
       <c r="F4" s="1">
-        <v>46226</v>
+        <v>46244</v>
       </c>
       <c r="G4">
-        <v>541715</v>
+        <v>522110</v>
       </c>
       <c r="H4" t="s">
         <v>31</v>
@@ -1429,182 +1432,179 @@
         <v>1</v>
       </c>
       <c r="J4" s="1">
-        <v>46289</v>
+        <v>46304</v>
       </c>
       <c r="K4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4" t="s">
         <v>32</v>
-      </c>
-      <c r="L4" t="s">
-        <v>20</v>
-      </c>
-      <c r="M4" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
         <v>34</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>35</v>
       </c>
       <c r="D5" t="s">
         <v>16</v>
       </c>
       <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="1">
+        <v>46226</v>
+      </c>
+      <c r="G5">
+        <v>541715</v>
+      </c>
+      <c r="H5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="1">
+        <v>46289</v>
+      </c>
+      <c r="K5" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="1">
-        <v>46213</v>
-      </c>
-      <c r="G5">
-        <v>493110</v>
-      </c>
-      <c r="H5" t="s">
-        <v>37</v>
-      </c>
-      <c r="I5">
-        <v>73</v>
-      </c>
-      <c r="J5" s="1">
-        <v>46273</v>
-      </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" t="s">
         <v>19</v>
-      </c>
-      <c r="L5" t="s">
-        <v>20</v>
-      </c>
-      <c r="M5" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
         <v>39</v>
       </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="F6" s="1">
+        <v>46213</v>
+      </c>
+      <c r="G6">
+        <v>493110</v>
+      </c>
+      <c r="H6" t="s">
         <v>40</v>
       </c>
-      <c r="D6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="I6">
+        <v>73</v>
+      </c>
+      <c r="J6" s="1">
+        <v>46273</v>
+      </c>
+      <c r="K6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M6" t="s">
         <v>41</v>
-      </c>
-      <c r="F6" s="1">
-        <v>46185</v>
-      </c>
-      <c r="G6">
-        <v>333415</v>
-      </c>
-      <c r="H6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I6">
-        <v>70</v>
-      </c>
-      <c r="J6" s="1">
-        <v>46264</v>
-      </c>
-      <c r="K6" t="s">
-        <v>32</v>
-      </c>
-      <c r="L6" t="s">
-        <v>20</v>
-      </c>
-      <c r="M6" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" t="s">
         <v>44</v>
       </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="F7" s="1">
+        <v>46185</v>
+      </c>
+      <c r="G7">
+        <v>333415</v>
+      </c>
+      <c r="H7" t="s">
         <v>45</v>
       </c>
-      <c r="D7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="1">
-        <v>46203</v>
-      </c>
-      <c r="G7">
-        <v>315250</v>
-      </c>
-      <c r="H7" t="s">
-        <v>46</v>
-      </c>
       <c r="I7">
-        <v>303</v>
+        <v>70</v>
       </c>
       <c r="J7" s="1">
         <v>46264</v>
       </c>
+      <c r="K7" t="s">
+        <v>36</v>
+      </c>
       <c r="L7" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="M7" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
         <v>48</v>
-      </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" t="s">
-        <v>49</v>
       </c>
       <c r="D8" t="s">
         <v>16</v>
       </c>
       <c r="E8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="1">
+        <v>46203</v>
+      </c>
+      <c r="G8">
+        <v>315250</v>
+      </c>
+      <c r="H8" t="s">
+        <v>49</v>
+      </c>
+      <c r="I8">
+        <v>303</v>
+      </c>
+      <c r="J8" s="1">
+        <v>46264</v>
+      </c>
+      <c r="L8" t="s">
         <v>50</v>
       </c>
-      <c r="F8" s="1">
-        <v>46202</v>
-      </c>
-      <c r="G8">
-        <v>561110</v>
-      </c>
-      <c r="H8" t="s">
-        <v>51</v>
-      </c>
-      <c r="I8">
-        <v>24</v>
-      </c>
-      <c r="J8" s="1">
-        <v>46262</v>
-      </c>
-      <c r="K8" t="s">
-        <v>32</v>
-      </c>
-      <c r="L8" t="s">
-        <v>20</v>
-      </c>
       <c r="M8" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
@@ -1613,39 +1613,39 @@
         <v>52</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="F9" s="1">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="G9">
-        <v>312111</v>
+        <v>561110</v>
       </c>
       <c r="H9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I9">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J9" s="1">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K9" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L9" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="M9" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -1654,28 +1654,34 @@
         <v>55</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="F10" s="1">
-        <v>46191</v>
+        <v>46199</v>
       </c>
       <c r="G10">
-        <v>424820</v>
+        <v>312111</v>
       </c>
       <c r="H10" t="s">
         <v>56</v>
       </c>
       <c r="I10">
-        <v>174</v>
+        <v>28</v>
       </c>
       <c r="J10" s="1">
-        <v>46251</v>
+        <v>46260</v>
+      </c>
+      <c r="K10" t="s">
+        <v>36</v>
+      </c>
+      <c r="L10" t="s">
+        <v>26</v>
       </c>
       <c r="M10" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
@@ -1689,115 +1695,112 @@
         <v>58</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E11" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="1">
+        <v>46191</v>
+      </c>
+      <c r="G11">
+        <v>424820</v>
+      </c>
+      <c r="H11" t="s">
         <v>59</v>
       </c>
-      <c r="F11" s="1">
-        <v>46189</v>
-      </c>
-      <c r="G11">
-        <v>812332</v>
-      </c>
-      <c r="H11" t="s">
-        <v>60</v>
-      </c>
       <c r="I11">
-        <v>32</v>
+        <v>174</v>
       </c>
       <c r="J11" s="1">
-        <v>46249</v>
-      </c>
-      <c r="K11" t="s">
-        <v>32</v>
-      </c>
-      <c r="L11" t="s">
-        <v>20</v>
+        <v>46251</v>
       </c>
       <c r="M11" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" t="s">
         <v>61</v>
       </c>
-      <c r="B12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" t="s">
         <v>62</v>
       </c>
-      <c r="D12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" t="s">
-        <v>36</v>
-      </c>
       <c r="F12" s="1">
-        <v>46237</v>
+        <v>46189</v>
       </c>
       <c r="G12">
-        <v>11141</v>
+        <v>812332</v>
       </c>
       <c r="H12" t="s">
         <v>63</v>
       </c>
       <c r="I12">
-        <v>127</v>
+        <v>32</v>
       </c>
       <c r="J12" s="1">
-        <v>46237</v>
+        <v>46249</v>
+      </c>
+      <c r="K12" t="s">
+        <v>36</v>
       </c>
       <c r="L12" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="M12" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D13" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E13" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F13" s="1">
-        <v>46149</v>
+        <v>46237</v>
       </c>
       <c r="G13">
-        <v>541715</v>
+        <v>11141</v>
       </c>
       <c r="H13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I13">
-        <v>3</v>
+        <v>127</v>
       </c>
       <c r="J13" s="1">
-        <v>46209</v>
+        <v>46237</v>
       </c>
       <c r="L13" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="M13" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
@@ -1806,72 +1809,69 @@
         <v>67</v>
       </c>
       <c r="D14" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="1">
+        <v>46149</v>
+      </c>
+      <c r="G14">
+        <v>541715</v>
+      </c>
+      <c r="H14" t="s">
         <v>68</v>
       </c>
-      <c r="F14" s="1">
-        <v>46142</v>
-      </c>
-      <c r="G14">
-        <v>321114</v>
-      </c>
-      <c r="H14" t="s">
-        <v>69</v>
-      </c>
       <c r="I14">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="J14" s="1">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="L14" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="M14" t="s">
-        <v>70</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" t="s">
         <v>71</v>
       </c>
-      <c r="B15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="F15" s="1">
+        <v>46142</v>
+      </c>
+      <c r="G15">
+        <v>321114</v>
+      </c>
+      <c r="H15" t="s">
         <v>72</v>
       </c>
-      <c r="D15" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" t="s">
-        <v>59</v>
-      </c>
-      <c r="F15" s="1">
-        <v>46141</v>
-      </c>
-      <c r="G15">
-        <v>722310</v>
-      </c>
-      <c r="H15" t="s">
+      <c r="I15">
+        <v>67</v>
+      </c>
+      <c r="J15" s="1">
+        <v>46204</v>
+      </c>
+      <c r="L15" t="s">
+        <v>26</v>
+      </c>
+      <c r="M15" t="s">
         <v>73</v>
-      </c>
-      <c r="I15">
-        <v>923</v>
-      </c>
-      <c r="J15" s="1">
-        <v>46203</v>
-      </c>
-      <c r="K15" t="s">
-        <v>32</v>
-      </c>
-      <c r="L15" t="s">
-        <v>47</v>
-      </c>
-      <c r="M15" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
@@ -1884,29 +1884,35 @@
       <c r="C16" t="s">
         <v>75</v>
       </c>
+      <c r="D16" t="s">
+        <v>16</v>
+      </c>
       <c r="E16" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F16" s="1">
-        <v>46147</v>
+        <v>46141</v>
       </c>
       <c r="G16">
-        <v>611310</v>
+        <v>722310</v>
       </c>
       <c r="H16" t="s">
         <v>76</v>
       </c>
       <c r="I16">
-        <v>36</v>
+        <v>923</v>
       </c>
       <c r="J16" s="1">
         <v>46203</v>
       </c>
+      <c r="K16" t="s">
+        <v>36</v>
+      </c>
       <c r="L16" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="M16" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
@@ -1919,11 +1925,8 @@
       <c r="C17" t="s">
         <v>78</v>
       </c>
-      <c r="D17" t="s">
-        <v>24</v>
-      </c>
       <c r="E17" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F17" s="1">
         <v>46147</v>
@@ -1935,16 +1938,16 @@
         <v>79</v>
       </c>
       <c r="I17">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="J17" s="1">
         <v>46203</v>
       </c>
       <c r="L17" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="M17" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
@@ -1958,31 +1961,31 @@
         <v>81</v>
       </c>
       <c r="D18" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E18" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="F18" s="1">
-        <v>46113</v>
+        <v>46147</v>
       </c>
       <c r="G18">
-        <v>488510</v>
+        <v>611310</v>
       </c>
       <c r="H18" t="s">
         <v>82</v>
       </c>
       <c r="I18">
-        <v>123</v>
+        <v>61</v>
       </c>
       <c r="J18" s="1">
-        <v>46179</v>
+        <v>46203</v>
       </c>
       <c r="L18" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="M18" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
@@ -1996,31 +1999,31 @@
         <v>84</v>
       </c>
       <c r="D19" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E19" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F19" s="1">
         <v>46113</v>
       </c>
       <c r="G19">
-        <v>492110</v>
+        <v>488510</v>
       </c>
       <c r="H19" t="s">
         <v>85</v>
       </c>
       <c r="I19">
-        <v>65</v>
+        <v>123</v>
       </c>
       <c r="J19" s="1">
-        <v>46175</v>
+        <v>46179</v>
       </c>
       <c r="L19" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="M19" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
@@ -2037,74 +2040,71 @@
         <v>16</v>
       </c>
       <c r="E20" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F20" s="1">
-        <v>46128</v>
+        <v>46113</v>
       </c>
       <c r="G20">
-        <v>56172</v>
+        <v>492110</v>
       </c>
       <c r="H20" t="s">
         <v>88</v>
       </c>
       <c r="I20">
-        <v>106</v>
+        <v>65</v>
       </c>
       <c r="J20" s="1">
-        <v>46152</v>
-      </c>
-      <c r="K20" t="s">
-        <v>32</v>
+        <v>46175</v>
+      </c>
+      <c r="L20" t="s">
+        <v>50</v>
       </c>
       <c r="M20" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="B21" t="s">
         <v>14</v>
       </c>
       <c r="C21" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D21" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E21" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="F21" s="1">
-        <v>46086</v>
+        <v>46128</v>
       </c>
       <c r="G21">
-        <v>541715</v>
+        <v>56172</v>
       </c>
       <c r="H21" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I21">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="J21" s="1">
-        <v>46148</v>
+        <v>46152</v>
       </c>
       <c r="K21" t="s">
-        <v>32</v>
-      </c>
-      <c r="L21" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="M21" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>91</v>
+        <v>33</v>
       </c>
       <c r="B22" t="s">
         <v>14</v>
@@ -2113,31 +2113,34 @@
         <v>92</v>
       </c>
       <c r="D22" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E22" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="F22" s="1">
-        <v>46077</v>
+        <v>46086</v>
       </c>
       <c r="G22">
-        <v>423120</v>
+        <v>541715</v>
       </c>
       <c r="H22" t="s">
         <v>93</v>
       </c>
       <c r="I22">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="J22" s="1">
-        <v>46142</v>
+        <v>46148</v>
+      </c>
+      <c r="K22" t="s">
+        <v>36</v>
       </c>
       <c r="L22" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="M22" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
@@ -2151,36 +2154,36 @@
         <v>95</v>
       </c>
       <c r="D23" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E23" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F23" s="1">
-        <v>46056</v>
+        <v>46077</v>
       </c>
       <c r="G23">
-        <v>541330</v>
+        <v>423120</v>
       </c>
       <c r="H23" t="s">
         <v>96</v>
       </c>
       <c r="I23">
-        <v>8</v>
+        <v>76</v>
       </c>
       <c r="J23" s="1">
-        <v>46128</v>
+        <v>46142</v>
       </c>
       <c r="L23" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="M23" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="B24" t="s">
         <v>14</v>
@@ -2189,308 +2192,308 @@
         <v>97</v>
       </c>
       <c r="D24" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E24" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F24" s="1">
-        <v>46051</v>
+        <v>46056</v>
       </c>
       <c r="G24">
-        <v>541715</v>
+        <v>541330</v>
       </c>
       <c r="H24" t="s">
         <v>98</v>
       </c>
       <c r="I24">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="J24" s="1">
-        <v>46114</v>
+        <v>46128</v>
       </c>
       <c r="L24" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="M24" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" t="s">
         <v>99</v>
-      </c>
-      <c r="B25" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" t="s">
-        <v>100</v>
       </c>
       <c r="D25" t="s">
         <v>16</v>
       </c>
       <c r="E25" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F25" s="1">
-        <v>46053</v>
+        <v>46051</v>
       </c>
       <c r="G25">
-        <v>517112</v>
+        <v>541715</v>
       </c>
       <c r="H25" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I25">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="J25" s="1">
         <v>46114</v>
       </c>
-      <c r="K25" t="s">
-        <v>32</v>
-      </c>
       <c r="L25" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="M25" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>101</v>
+      </c>
+      <c r="B26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" t="s">
         <v>102</v>
       </c>
-      <c r="B26" t="s">
-        <v>14</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" t="s">
+        <v>53</v>
+      </c>
+      <c r="F26" s="1">
+        <v>46053</v>
+      </c>
+      <c r="G26">
+        <v>517112</v>
+      </c>
+      <c r="H26" t="s">
         <v>103</v>
       </c>
-      <c r="D26" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" t="s">
-        <v>104</v>
-      </c>
-      <c r="F26" s="1">
-        <v>46007</v>
-      </c>
-      <c r="G26">
-        <v>335911</v>
-      </c>
-      <c r="H26" t="s">
-        <v>105</v>
-      </c>
       <c r="I26">
-        <v>1514</v>
+        <v>74</v>
       </c>
       <c r="J26" s="1">
-        <v>46112</v>
+        <v>46114</v>
+      </c>
+      <c r="K26" t="s">
+        <v>36</v>
       </c>
       <c r="L26" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="M26" t="s">
-        <v>106</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B27" t="s">
         <v>14</v>
       </c>
       <c r="C27" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D27" t="s">
         <v>16</v>
       </c>
       <c r="E27" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F27" s="1">
-        <v>46057</v>
+        <v>46007</v>
       </c>
       <c r="G27">
-        <v>541611</v>
+        <v>335911</v>
       </c>
       <c r="H27" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="I27">
-        <v>1</v>
+        <v>1514</v>
       </c>
       <c r="J27" s="1">
         <v>46112</v>
       </c>
       <c r="L27" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="M27" t="s">
-        <v>33</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="B28" t="s">
         <v>14</v>
       </c>
       <c r="C28" t="s">
+        <v>110</v>
+      </c>
+      <c r="D28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" t="s">
         <v>111</v>
       </c>
-      <c r="D28" t="s">
-        <v>24</v>
-      </c>
-      <c r="E28" t="s">
-        <v>30</v>
-      </c>
       <c r="F28" s="1">
-        <v>46034</v>
+        <v>46057</v>
       </c>
       <c r="G28">
-        <v>541330</v>
+        <v>541611</v>
       </c>
       <c r="H28" t="s">
         <v>112</v>
       </c>
       <c r="I28">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="J28" s="1">
-        <v>46107</v>
+        <v>46112</v>
       </c>
       <c r="L28" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="M28" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" t="s">
         <v>113</v>
-      </c>
-      <c r="B29" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" t="s">
-        <v>114</v>
       </c>
       <c r="D29" t="s">
         <v>16</v>
       </c>
       <c r="E29" t="s">
-        <v>115</v>
+        <v>17</v>
       </c>
       <c r="F29" s="1">
-        <v>46098</v>
+        <v>46034</v>
       </c>
       <c r="G29">
-        <v>33331</v>
+        <v>541330</v>
       </c>
       <c r="H29" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I29">
-        <v>114</v>
+        <v>42</v>
       </c>
       <c r="J29" s="1">
-        <v>46105</v>
-      </c>
-      <c r="K29" t="s">
+        <v>46107</v>
+      </c>
+      <c r="L29" t="s">
+        <v>26</v>
+      </c>
+      <c r="M29" t="s">
         <v>19</v>
-      </c>
-      <c r="L29" t="s">
-        <v>47</v>
-      </c>
-      <c r="M29" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>115</v>
+      </c>
+      <c r="B30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" t="s">
+        <v>116</v>
+      </c>
+      <c r="D30" t="s">
+        <v>22</v>
+      </c>
+      <c r="E30" t="s">
         <v>117</v>
       </c>
-      <c r="B30" t="s">
-        <v>14</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="F30" s="1">
+        <v>46098</v>
+      </c>
+      <c r="G30">
+        <v>33331</v>
+      </c>
+      <c r="H30" t="s">
         <v>118</v>
       </c>
-      <c r="D30" t="s">
-        <v>24</v>
-      </c>
-      <c r="E30" t="s">
-        <v>30</v>
-      </c>
-      <c r="F30" s="1">
-        <v>46041</v>
-      </c>
-      <c r="G30">
-        <v>541330</v>
-      </c>
-      <c r="H30" t="s">
-        <v>119</v>
-      </c>
       <c r="I30">
-        <v>33</v>
+        <v>114</v>
       </c>
       <c r="J30" s="1">
-        <v>46101</v>
+        <v>46105</v>
+      </c>
+      <c r="K30" t="s">
+        <v>25</v>
       </c>
       <c r="L30" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="M30" t="s">
-        <v>33</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>119</v>
+      </c>
+      <c r="B31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" t="s">
         <v>120</v>
-      </c>
-      <c r="B31" t="s">
-        <v>14</v>
-      </c>
-      <c r="C31" t="s">
-        <v>121</v>
       </c>
       <c r="D31" t="s">
         <v>16</v>
       </c>
       <c r="E31" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F31" s="1">
-        <v>46087</v>
+        <v>46041</v>
       </c>
       <c r="G31">
-        <v>545410</v>
+        <v>541330</v>
       </c>
       <c r="H31" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I31">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="J31" s="1">
-        <v>46087</v>
+        <v>46101</v>
       </c>
       <c r="L31" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="M31" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>28</v>
+        <v>122</v>
       </c>
       <c r="B32" t="s">
         <v>14</v>
@@ -2499,36 +2502,36 @@
         <v>123</v>
       </c>
       <c r="D32" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E32" t="s">
         <v>30</v>
       </c>
       <c r="F32" s="1">
-        <v>46027</v>
+        <v>46087</v>
       </c>
       <c r="G32">
-        <v>541715</v>
+        <v>545410</v>
       </c>
       <c r="H32" t="s">
         <v>124</v>
       </c>
       <c r="I32">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="J32" s="1">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="L32" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="M32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B33" t="s">
         <v>14</v>
@@ -2537,13 +2540,13 @@
         <v>125</v>
       </c>
       <c r="D33" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E33" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F33" s="1">
-        <v>46008</v>
+        <v>46027</v>
       </c>
       <c r="G33">
         <v>541715</v>
@@ -2552,62 +2555,59 @@
         <v>126</v>
       </c>
       <c r="I33">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="J33" s="1">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="L33" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="M33" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" t="s">
         <v>127</v>
       </c>
-      <c r="B34" t="s">
-        <v>14</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
+        <v>16</v>
+      </c>
+      <c r="E34" t="s">
+        <v>17</v>
+      </c>
+      <c r="F34" s="1">
+        <v>46008</v>
+      </c>
+      <c r="G34">
+        <v>541715</v>
+      </c>
+      <c r="H34" t="s">
         <v>128</v>
       </c>
-      <c r="D34" t="s">
-        <v>24</v>
-      </c>
-      <c r="E34" t="s">
-        <v>36</v>
-      </c>
-      <c r="F34" s="1">
-        <v>46006</v>
-      </c>
-      <c r="G34">
-        <v>332991</v>
-      </c>
-      <c r="H34" t="s">
-        <v>129</v>
-      </c>
       <c r="I34">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="J34" s="1">
-        <v>46066</v>
-      </c>
-      <c r="K34" t="s">
+        <v>46071</v>
+      </c>
+      <c r="L34" t="s">
+        <v>26</v>
+      </c>
+      <c r="M34" t="s">
         <v>19</v>
-      </c>
-      <c r="L34" t="s">
-        <v>47</v>
-      </c>
-      <c r="M34" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>94</v>
+        <v>129</v>
       </c>
       <c r="B35" t="s">
         <v>14</v>
@@ -2616,31 +2616,72 @@
         <v>130</v>
       </c>
       <c r="D35" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E35" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F35" s="1">
         <v>46006</v>
       </c>
       <c r="G35">
-        <v>541330</v>
+        <v>332991</v>
       </c>
       <c r="H35" t="s">
         <v>131</v>
       </c>
       <c r="I35">
+        <v>77</v>
+      </c>
+      <c r="J35" s="1">
+        <v>46066</v>
+      </c>
+      <c r="K35" t="s">
+        <v>25</v>
+      </c>
+      <c r="L35" t="s">
+        <v>50</v>
+      </c>
+      <c r="M35" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>13</v>
+      </c>
+      <c r="B36" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" t="s">
+        <v>132</v>
+      </c>
+      <c r="D36" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" t="s">
+        <v>17</v>
+      </c>
+      <c r="F36" s="1">
+        <v>46006</v>
+      </c>
+      <c r="G36">
+        <v>541330</v>
+      </c>
+      <c r="H36" t="s">
+        <v>133</v>
+      </c>
+      <c r="I36">
         <v>32</v>
       </c>
-      <c r="J35" s="1">
+      <c r="J36" s="1">
         <v>46038</v>
       </c>
-      <c r="L35" t="s">
-        <v>20</v>
-      </c>
-      <c r="M35" t="s">
-        <v>33</v>
+      <c r="L36" t="s">
+        <v>26</v>
+      </c>
+      <c r="M36" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -2824,13 +2865,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41A5448D-99F8-4FA6-80D5-BF0375E6D9BF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B742522-8053-4383-B942-EB4F999B5AB7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00DB289B-4FC3-407A-A3BE-4467ECAEF91B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A16AA87B-3F26-4084-8B3D-A988F4450491}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A239435C-27B1-4E10-AB9A-3AFADEEB1F57}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD310412-3761-4564-AE70-85BFDE8393B3}"/>
 </file>
--- a/data/warn-scraper/cache/ky/latest.xlsx
+++ b/data/warn-scraper/cache/ky/latest.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileSharing readOnlyRecommended="1"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeff.lee\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kymsoffice-my.sharepoint.com/personal/erin_white_ky_gov/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C636E9C6-D354-4F7A-A5A2-ECC3BA645240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E362714-CD64-46B0-A879-C214B04C2E38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="cON/fOB+pXT38WAaMTDr3XRFD5vwFv44BbsiO7IvvpgClL/nirDMlrGaeEHNR1NhtkmCeHcA4DzDlg7pukO/Xg==" workbookSaltValue="qY4e9rS654nIwJXKKpqDzA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="7176" yWindow="900" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19390" yWindow="290" windowWidth="33570" windowHeight="19690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WARN Report" sheetId="1" r:id="rId1"/>
@@ -3462,13 +3464,45 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1368E410-9E68-422B-AA21-14845086F8C6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1368E410-9E68-422B-AA21-14845086F8C6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="ac1070bf-3ce6-4b87-ab2d-f70092a0dc57"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{710C0438-4B0B-41DB-9EF5-3B63B27D813E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{710C0438-4B0B-41DB-9EF5-3B63B27D813E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AB2E7E6-2EFA-4AC5-8B9D-85CFB84C1F3B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AB2E7E6-2EFA-4AC5-8B9D-85CFB84C1F3B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ac1070bf-3ce6-4b87-ab2d-f70092a0dc57"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>